--- a/Visualizaciòn de datos/Entrega 1/Entrega 1.xlsx
+++ b/Visualizaciòn de datos/Entrega 1/Entrega 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ee31e4a3756f50f/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3ee31e4a3756f50f/Escritorio/facultad/Visualizaciòn de datos/Entrega 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_A22F17F901E5292FE97333AE6E7D9633C96E1354" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D6587B-5F22-41B2-BF11-ADD655E62396}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_A22F17F901E5292FE97333AE6E7D9633C96E1354" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE835C4A-1AE8-4380-806F-594FA65BB682}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
-    <t>La pandemia aceleró el fin de la atención presencial al ciudadano</t>
-  </si>
-  <si>
     <t>Composición de canales de atención ciudadana — 2016 a 2025 · % del total anual</t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>Digital</t>
+  </si>
+  <si>
+    <t>La pandemia aceleró la digitalización en la atención al ciudadano</t>
   </si>
 </sst>
 </file>
@@ -215,11 +215,6 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,6 +243,11 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1357,198 +1357,198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="B3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="B4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:6" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>16</v>
+      <c r="E6" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="10">
+      <c r="B7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="7">
         <v>0.74199999999999999</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="7">
         <v>0.23</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="7">
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="12">
+      <c r="B8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="9">
         <v>0.63900000000000001</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="9">
         <v>0.315</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="9">
         <v>4.7E-2</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="10">
+      <c r="B9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7">
         <v>0.504</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="7">
         <v>0.373</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="7">
         <v>0.123</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="12">
+      <c r="B10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="9">
         <v>0.46</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="9">
         <v>0.374</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="9">
         <v>0.16600000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="10">
+      <c r="B11" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="7">
         <v>0.28499999999999998</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="7">
         <v>0.27800000000000002</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="7">
         <v>0.438</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="12">
+      <c r="B12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="9">
         <v>0.224</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="9">
         <v>0.307</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="9">
         <v>0.47</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="10">
+      <c r="B13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="7">
         <v>0.24099999999999999</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="7">
         <v>0.36799999999999999</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="7">
         <v>0.39100000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="12">
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="9">
         <v>0.186</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="9">
         <v>0.41899999999999998</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="9">
         <v>0.39600000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="10">
+      <c r="B15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="7">
         <v>0.219</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="7">
         <v>0.4</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="7">
         <v>0.38100000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="12">
+      <c r="B16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="9">
         <v>0.17199999999999999</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="9">
         <v>0.44900000000000001</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="9">
         <v>0.379</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="B17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
     </row>
     <row r="18" spans="2:5" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
